--- a/Tarea-4/Diccionarios/20261-bd1-g100-tia-04-E-X-resultados.xlsx
+++ b/Tarea-4/Diccionarios/20261-bd1-g100-tia-04-E-X-resultados.xlsx
@@ -1,17 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30014"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23D1533-D9F7-4446-A2C7-CCF436316533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-33495" yWindow="-540" windowWidth="27555" windowHeight="15495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Tipos de Dato" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Invetario de Tablas" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Diccionario Datos - PostgreSQL" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Diccionario Datos - MySQL" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Diccionario Datos - MS SQL Serv" sheetId="5" r:id="rId8"/>
+    <sheet name="Tipos de Dato" sheetId="1" r:id="rId1"/>
+    <sheet name="Invetario de Tablas" sheetId="2" r:id="rId2"/>
+    <sheet name="Diccionario Datos - PostgreSQL" sheetId="3" r:id="rId3"/>
+    <sheet name="Diccionario Datos - MySQL" sheetId="4" r:id="rId4"/>
+    <sheet name="Diccionario Datos - MS SQL Serv" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="/gH4XWYhxTR8MV825D2AG38Xm92QnBKPP77+o2APUu4="/>
     </ext>
@@ -20,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="113">
   <si>
     <t>Tipos de Datos - Tabla Comparativa</t>
   </si>
@@ -41,9 +59,6 @@
   </si>
   <si>
     <t>En MS SQL Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versión: </t>
   </si>
   <si>
     <t>AUTOINCREMENTABLE</t>
@@ -170,52 +185,52 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFB45F06"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Puede seguir agregando tablas. Solamente tiene que copiar y pegar hacia abajo hasta que complete todas las tablas 
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>OJO - ATENCIÓN</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF980000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> - RECUERDE COLOCAR LAS REFERENCIAS DE  LAS TABLAS</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF0000FF"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>NÚMERO , NOMBRE, DESCRIPCIóN</t>
     </r>
@@ -229,52 +244,52 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFB45F06"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Puede seguir agregando tablas. Solamente tiene que copiar y pegar hacia abajo hasta que complete todas las tablas 
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>OJO - ATENCIÓN</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF980000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> - RECUERDE COLOCAR LAS REFERENCIAS DE  LAS TABLAS</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF0000FF"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>NÚMERO , NOMBRE, DESCRIPCIóN</t>
     </r>
@@ -291,173 +306,543 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFB45F06"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Puede seguir agregando tablas. Solamente tiene que copiar y pegar hacia abajo hasta que complete todas las tablas 
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>OJO - ATENCIÓN</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF980000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> - RECUERDE COLOCAR LAS REFERENCIAS DE  LAS TABLAS</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FFFF0000"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
         <i/>
+        <sz val="17"/>
         <color rgb="FF0000FF"/>
-        <sz val="17.0"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>NÚMERO , NOMBRE, DESCRIPCIóN</t>
     </r>
+  </si>
+  <si>
+    <t>Identificador numérico que crece automáticamente.</t>
+  </si>
+  <si>
+    <r>
+      <t>SERIAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>GENERATED ALWAYS AS IDENTITY</t>
+    </r>
+  </si>
+  <si>
+    <t>INT AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>INT IDENTITY(1,1)</t>
+  </si>
+  <si>
+    <t>Identificador único universal de 128 bits.</t>
+  </si>
+  <si>
+    <r>
+      <t>UUID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>BINARY(16)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>UNIQUEIDENTIFIER</t>
+  </si>
+  <si>
+    <t>Número sin decimales (32 bits estándar).</t>
+  </si>
+  <si>
+    <t>INTEGER</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>Número de precisión exacta para cálculos financieros.</t>
+  </si>
+  <si>
+    <r>
+      <t>NUMERIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+  </si>
+  <si>
+    <t>Valores booleanos (Verdadero/Falso).</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <r>
+      <t>TINYINT(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>BOOL</t>
+    </r>
+  </si>
+  <si>
+    <t>BIT</t>
+  </si>
+  <si>
+    <t>Cadena de caracteres de longitud variable ilimitada.</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>LONGTEXT</t>
+  </si>
+  <si>
+    <t>NVARCHAR(MAX)</t>
+  </si>
+  <si>
+    <t>Caracteres de longitud fija.</t>
+  </si>
+  <si>
+    <t>CHAR(n)</t>
+  </si>
+  <si>
+    <t>NCHAR(n)</t>
+  </si>
+  <si>
+    <t>Almacena solo día, mes y año.</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Almacena fecha y hora en un solo campo.</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>DATETIME2</t>
+  </si>
+  <si>
+    <t>Almacena solo la hora.</t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>Dirección web (cadena de texto larga).</t>
+  </si>
+  <si>
+    <r>
+      <t>TEXT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+  </si>
+  <si>
+    <t>VARCHAR(2083)</t>
+  </si>
+  <si>
+    <t>NVARCHAR(2048)</t>
+  </si>
+  <si>
+    <t>Lista de valores permitidos predefinidos.</t>
+  </si>
+  <si>
+    <t>CREATE TYPE ... AS ENUM</t>
+  </si>
+  <si>
+    <t>ENUM('v1', 'v2')</t>
+  </si>
+  <si>
+    <t>(Usa CHECK Constraint)</t>
+  </si>
+  <si>
+    <t>Cadena de longitud variable (máx 255).</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>NVARCHAR(255)</t>
+  </si>
+  <si>
+    <t>Datos binarios de longitud variable.</t>
+  </si>
+  <si>
+    <t>BYTEA</t>
+  </si>
+  <si>
+    <r>
+      <t>VARBINARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>BLOB</t>
+    </r>
+  </si>
+  <si>
+    <t>VARBINARY</t>
+  </si>
+  <si>
+    <t>Texto con formato JSON estándar.</t>
+  </si>
+  <si>
+    <r>
+      <t>NVARCHAR(MAX)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (con validación JSON)</t>
+    </r>
+  </si>
+  <si>
+    <t>JSON en formato binario optimizado para búsqueda.</t>
+  </si>
+  <si>
+    <t>(Nativo en JSON)</t>
+  </si>
+  <si>
+    <t>(Usa JSON en NVARCHAR)</t>
+  </si>
+  <si>
+    <t>Archivos de imagen en la base de datos.</t>
+  </si>
+  <si>
+    <t>LONGBLOB</t>
+  </si>
+  <si>
+    <t>VARBINARY(MAX)</t>
+  </si>
+  <si>
+    <t>Archivos de sonido en la base de datos.</t>
+  </si>
+  <si>
+    <t>Versión:  16+</t>
+  </si>
+  <si>
+    <t>Versión: 8.0+</t>
+  </si>
+  <si>
+    <t>Versión: 2022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="26">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
-      <sz val="12.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="17"/>
+      <color rgb="FFB45F06"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="17"/>
+      <color rgb="FF980000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="17"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -465,7 +850,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -522,42 +907,55 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
-    <border/>
+  <borders count="40">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -567,6 +965,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -581,27 +980,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -611,6 +1017,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -625,6 +1032,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -639,6 +1047,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -653,8 +1062,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -664,27 +1075,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -694,6 +1112,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -708,6 +1127,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -722,19 +1142,23 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -744,6 +1168,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -758,27 +1183,34 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -788,6 +1220,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -796,6 +1229,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -807,66 +1243,99 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -875,273 +1344,295 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+  <cellXfs count="85">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="10" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="20" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="31" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf borderId="6" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf borderId="9" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf borderId="35" fillId="7" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="35" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="36" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="38" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1331,312 +1822,464 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:K988"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.0"/>
-    <col customWidth="1" min="2" max="2" width="29.5"/>
-    <col customWidth="1" min="3" max="3" width="45.63"/>
-    <col customWidth="1" min="4" max="4" width="34.5"/>
-    <col customWidth="1" min="5" max="5" width="26.63"/>
-    <col customWidth="1" min="6" max="6" width="30.88"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" customWidth="1"/>
+    <col min="4" max="4" width="34.44140625" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="38.25" customHeight="1">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="36" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="30.0" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+    <row r="3" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="84" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="84" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="84" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="C4" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="82" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A5" s="6">
+        <f t="shared" ref="A5:A21" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="82" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A7" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="82" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="82" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="B10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" ht="30.0" customHeight="1">
-      <c r="A5" s="11">
-        <f t="shared" ref="A5:A21" si="1">A4+1</f>
-        <v>2</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="11">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="B12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="11">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="11">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="B14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" thickBot="1">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="11">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" thickBot="1">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="11">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="B17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" ht="30.0" customHeight="1">
-      <c r="A12" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="B18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" ht="30.0" customHeight="1">
-      <c r="A13" s="11">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="B19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A20" s="6">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" ht="30.0" customHeight="1">
-      <c r="A14" s="11">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="B20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A21" s="6">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="11">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="11">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" ht="27.75" customHeight="1">
-      <c r="A18" s="11">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" ht="27.75" customHeight="1">
-      <c r="A19" s="11">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" ht="27.75" customHeight="1">
-      <c r="A20" s="11">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B20" s="12" t="s">
+      <c r="B21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" ht="27.75" customHeight="1">
-      <c r="A21" s="11">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="C21" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="82" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2598,293 +3241,301 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.0"/>
-    <col customWidth="1" min="2" max="2" width="37.38"/>
-    <col customWidth="1" min="3" max="3" width="71.88"/>
-    <col customWidth="1" min="4" max="4" width="58.63"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="71.88671875" customWidth="1"/>
+    <col min="4" max="4" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:9" ht="28.5" customHeight="1">
+      <c r="A1" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="69" customHeight="1">
+      <c r="A2" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" ht="69.0" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="36" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" ht="36.0" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" ht="37.5" customHeight="1">
-      <c r="A4" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A5" s="6">
+        <f t="shared" ref="A5:A28" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="20"/>
-    </row>
-    <row r="5" ht="37.5" customHeight="1">
-      <c r="A5" s="11">
-        <f t="shared" ref="A5:A28" si="1">A4+1</f>
-        <v>2</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="C5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="20"/>
-    </row>
-    <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="11">
-        <f t="shared" si="1"/>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-    </row>
-    <row r="7" ht="37.5" customHeight="1">
-      <c r="A7" s="11">
-        <f t="shared" si="1"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A7" s="6">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-    </row>
-    <row r="8" ht="37.5" customHeight="1">
-      <c r="A8" s="11">
-        <f t="shared" si="1"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9" ht="37.5" customHeight="1">
-      <c r="A9" s="11">
-        <f t="shared" si="1"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" ht="37.5" customHeight="1">
-      <c r="A10" s="11">
-        <f t="shared" si="1"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-    </row>
-    <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="11">
-        <f t="shared" si="1"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="11">
-        <f t="shared" si="1"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-    </row>
-    <row r="13" ht="37.5" customHeight="1">
-      <c r="A13" s="11">
-        <f t="shared" si="1"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-    </row>
-    <row r="14" ht="37.5" customHeight="1">
-      <c r="A14" s="11">
-        <f t="shared" si="1"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-    </row>
-    <row r="15" ht="37.5" customHeight="1">
-      <c r="A15" s="11">
-        <f t="shared" si="1"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-    </row>
-    <row r="16" ht="37.5" customHeight="1">
-      <c r="A16" s="11">
-        <f t="shared" si="1"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-    </row>
-    <row r="17" ht="37.5" customHeight="1">
-      <c r="A17" s="11">
-        <f t="shared" si="1"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-    </row>
-    <row r="18" ht="37.5" customHeight="1">
-      <c r="A18" s="11">
-        <f t="shared" si="1"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-    </row>
-    <row r="19" ht="37.5" customHeight="1">
-      <c r="A19" s="11">
-        <f t="shared" si="1"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-    </row>
-    <row r="20" ht="37.5" customHeight="1">
-      <c r="A20" s="11">
-        <f t="shared" si="1"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A20" s="6">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-    </row>
-    <row r="21" ht="37.5" customHeight="1">
-      <c r="A21" s="11">
-        <f t="shared" si="1"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A21" s="6">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-    </row>
-    <row r="22" ht="37.5" customHeight="1">
-      <c r="A22" s="11">
-        <f t="shared" si="1"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A22" s="6">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-    </row>
-    <row r="23" ht="37.5" customHeight="1">
-      <c r="A23" s="11">
-        <f t="shared" si="1"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A23" s="6">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-    </row>
-    <row r="24" ht="37.5" customHeight="1">
-      <c r="A24" s="11">
-        <f t="shared" si="1"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A24" s="6">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-    </row>
-    <row r="25" ht="37.5" customHeight="1">
-      <c r="A25" s="11">
-        <f t="shared" si="1"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+    </row>
+    <row r="25" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A25" s="6">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-    </row>
-    <row r="26" ht="37.5" customHeight="1">
-      <c r="A26" s="11">
-        <f t="shared" si="1"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A26" s="6">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-    </row>
-    <row r="27" ht="37.5" customHeight="1">
-      <c r="A27" s="11">
-        <f t="shared" si="1"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A27" s="6">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-    </row>
-    <row r="28" ht="37.5" customHeight="1">
-      <c r="A28" s="11">
-        <f t="shared" si="1"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A28" s="6">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -3859,710 +4510,735 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y971"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="33.75"/>
-    <col customWidth="1" min="3" max="3" width="13.38"/>
-    <col customWidth="1" min="4" max="5" width="3.88"/>
-    <col customWidth="1" min="6" max="6" width="21.63"/>
-    <col customWidth="1" min="7" max="9" width="3.88"/>
-    <col customWidth="1" min="10" max="10" width="20.25"/>
-    <col customWidth="1" min="11" max="22" width="3.88"/>
-    <col customWidth="1" min="23" max="23" width="4.63"/>
-    <col customWidth="1" min="24" max="24" width="17.0"/>
-    <col customWidth="1" min="25" max="25" width="30.38"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="5" width="3.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
+    <col min="7" max="9" width="3.88671875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="22" width="3.88671875" customWidth="1"/>
+    <col min="23" max="23" width="4.6640625" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.0" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" ht="28.5" customHeight="1"/>
-    <row r="3" ht="62.25" customHeight="1">
-      <c r="A3" s="23">
+    <row r="1" spans="1:25" ht="39" customHeight="1">
+      <c r="A1" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+    </row>
+    <row r="2" spans="1:25" ht="28.5" customHeight="1"/>
+    <row r="3" spans="1:25" ht="62.25" customHeight="1">
+      <c r="A3" s="11">
         <f>'Invetario de Tablas'!A4</f>
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="25" t="str">
+      <c r="B3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="50" t="str">
         <f>'Invetario de Tablas'!B4</f>
         <v>ejemplo tabla 1</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="28" t="str">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="54" t="str">
         <f>'Invetario de Tablas'!C4</f>
         <v>ejemplo derscripción tabla 1</v>
       </c>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="29" t="s">
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="14"/>
+    </row>
+    <row r="4" spans="1:25" ht="42.75" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="30"/>
-    </row>
-    <row r="4" ht="42.75" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="C4" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="41"/>
+      <c r="T4" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="41"/>
+      <c r="V4" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="41"/>
+      <c r="X4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="45"/>
+    </row>
+    <row r="5" spans="1:25" ht="30" customHeight="1">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="9"/>
-      <c r="X4" s="32" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="45"/>
+    </row>
+    <row r="6" spans="1:25" ht="30" customHeight="1">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="45"/>
+    </row>
+    <row r="7" spans="1:25" ht="30" customHeight="1">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="45"/>
+    </row>
+    <row r="8" spans="1:25" ht="30" customHeight="1">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="45"/>
+    </row>
+    <row r="9" spans="1:25" ht="30" customHeight="1">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="45"/>
+    </row>
+    <row r="10" spans="1:25" ht="30" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="45"/>
+    </row>
+    <row r="11" spans="1:25" ht="30" customHeight="1">
+      <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="33"/>
-    </row>
-    <row r="5" ht="30.0" customHeight="1">
-      <c r="A5" s="34">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="33"/>
-    </row>
-    <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="34">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="33"/>
-    </row>
-    <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="34">
-        <v>3.0</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="33"/>
-    </row>
-    <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="34">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="33"/>
-    </row>
-    <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="34">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="33"/>
-    </row>
-    <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="33"/>
-    </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="34" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="45"/>
+    </row>
+    <row r="12" spans="1:25" ht="28.5" customHeight="1">
+      <c r="A12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="33"/>
-    </row>
-    <row r="12" ht="28.5" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="40"/>
-    </row>
-    <row r="13" ht="36.0" customHeight="1"/>
-    <row r="14" ht="54.0" customHeight="1">
-      <c r="A14" s="23">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="49"/>
+    </row>
+    <row r="13" spans="1:25" ht="36" customHeight="1"/>
+    <row r="14" spans="1:25" ht="54" customHeight="1">
+      <c r="A14" s="11">
         <f>'Invetario de Tablas'!A5</f>
         <v>2</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="25" t="str">
+      <c r="B14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="50" t="str">
         <f>'Invetario de Tablas'!B5</f>
         <v>ejemplo tabla 2</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="28" t="str">
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="54" t="str">
         <f>'Invetario de Tablas'!C5</f>
         <v>ejemplo derscripción tabla 2</v>
       </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="29" t="s">
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y14" s="14"/>
+    </row>
+    <row r="15" spans="1:25" ht="60" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Y14" s="30"/>
-    </row>
-    <row r="15" ht="60.0" customHeight="1">
-      <c r="A15" s="31" t="s">
+      <c r="C15" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="S15" s="41"/>
+      <c r="T15" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="41"/>
+      <c r="V15" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" s="41"/>
+      <c r="X15" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="45"/>
+    </row>
+    <row r="16" spans="1:25" ht="30" customHeight="1">
+      <c r="A16" s="19">
         <v>1</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="S15" s="9"/>
-      <c r="T15" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="U15" s="9"/>
-      <c r="V15" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="W15" s="9"/>
-      <c r="X15" s="32" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="45"/>
+    </row>
+    <row r="17" spans="1:25" ht="30" customHeight="1">
+      <c r="A17" s="19">
+        <v>2</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="45"/>
+    </row>
+    <row r="18" spans="1:25" ht="30" customHeight="1">
+      <c r="A18" s="19">
+        <v>3</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="45"/>
+    </row>
+    <row r="19" spans="1:25" ht="30" customHeight="1">
+      <c r="A19" s="19">
+        <v>4</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="45"/>
+    </row>
+    <row r="20" spans="1:25" ht="30" customHeight="1">
+      <c r="A20" s="19">
+        <v>5</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="44"/>
+      <c r="Y20" s="45"/>
+    </row>
+    <row r="21" spans="1:25" ht="30" customHeight="1">
+      <c r="A21" s="20"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="45"/>
+    </row>
+    <row r="22" spans="1:25" ht="30" customHeight="1">
+      <c r="A22" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="Y15" s="33"/>
-    </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="33"/>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="33"/>
-    </row>
-    <row r="18" ht="30.0" customHeight="1">
-      <c r="A18" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="33"/>
-    </row>
-    <row r="19" ht="30.0" customHeight="1">
-      <c r="A19" s="41">
-        <v>4.0</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="33"/>
-    </row>
-    <row r="20" ht="30.0" customHeight="1">
-      <c r="A20" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="33"/>
-    </row>
-    <row r="21" ht="30.0" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="33"/>
-    </row>
-    <row r="22" ht="30.0" customHeight="1">
-      <c r="A22" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="40"/>
-    </row>
-    <row r="23" ht="48.0" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-    </row>
-    <row r="24" ht="40.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="9"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="49"/>
+    </row>
+    <row r="23" spans="1:25" ht="48" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+    </row>
+    <row r="24" spans="1:25" ht="40.5" customHeight="1">
+      <c r="A24" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="41"/>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -5504,29 +6180,102 @@
     <row r="971" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="137">
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:W3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="A24:Y24"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="O11:Q11"/>
@@ -5545,795 +6294,757 @@
     <mergeCell ref="K14:W14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="A24:Y24"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:W3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y971"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="29.75"/>
-    <col customWidth="1" min="3" max="3" width="32.13"/>
-    <col customWidth="1" min="4" max="9" width="3.88"/>
-    <col customWidth="1" min="10" max="10" width="23.5"/>
-    <col customWidth="1" min="11" max="22" width="3.88"/>
-    <col customWidth="1" min="23" max="23" width="4.63"/>
-    <col customWidth="1" min="24" max="24" width="17.0"/>
-    <col customWidth="1" min="25" max="25" width="30.38"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" customWidth="1"/>
+    <col min="4" max="9" width="3.88671875" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" customWidth="1"/>
+    <col min="11" max="22" width="3.88671875" customWidth="1"/>
+    <col min="23" max="23" width="4.6640625" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.0" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" ht="28.5" customHeight="1"/>
-    <row r="3" ht="52.5" customHeight="1">
-      <c r="A3" s="50">
+    <row r="1" spans="1:25" ht="39" customHeight="1">
+      <c r="A1" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+    </row>
+    <row r="2" spans="1:25" ht="28.5" customHeight="1"/>
+    <row r="3" spans="1:25" ht="52.5" customHeight="1">
+      <c r="A3" s="24">
         <f>'Invetario de Tablas'!A4</f>
         <v>1</v>
       </c>
-      <c r="B3" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="52" t="str">
+      <c r="B3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="69" t="str">
         <f>'Invetario de Tablas'!B4</f>
         <v>ejemplo tabla 1</v>
       </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="55" t="str">
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="71" t="str">
         <f>'Invetario de Tablas'!C4</f>
         <v>ejemplo derscripción tabla 1</v>
       </c>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="56" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="61"/>
+      <c r="X3" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="14"/>
+    </row>
+    <row r="4" spans="1:25" ht="35.25" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="30"/>
-    </row>
-    <row r="4" ht="35.25" customHeight="1">
-      <c r="A4" s="57" t="s">
+      <c r="C4" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="63"/>
+      <c r="T4" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="63"/>
+      <c r="V4" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="63"/>
+      <c r="X4" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="65"/>
+    </row>
+    <row r="5" spans="1:25" ht="30" customHeight="1">
+      <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="B4" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="60"/>
-      <c r="O4" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="60"/>
-      <c r="T4" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" s="60"/>
-      <c r="V4" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="61"/>
+    </row>
+    <row r="6" spans="1:25" ht="30" customHeight="1">
+      <c r="A6" s="29">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="59"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="61"/>
+    </row>
+    <row r="7" spans="1:25" ht="30" customHeight="1">
+      <c r="A7" s="29">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="59"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="59"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="59"/>
+      <c r="Y7" s="61"/>
+    </row>
+    <row r="8" spans="1:25" ht="30" customHeight="1">
+      <c r="A8" s="29">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="59"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="59"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="59"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="59"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="61"/>
+    </row>
+    <row r="9" spans="1:25" ht="30" customHeight="1">
+      <c r="A9" s="29">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="59"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="59"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="59"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="59"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="61"/>
+    </row>
+    <row r="10" spans="1:25" ht="30" customHeight="1">
+      <c r="A10" s="31"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="59"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="59"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="61"/>
+    </row>
+    <row r="11" spans="1:25" ht="30" customHeight="1">
+      <c r="A11" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="64"/>
-    </row>
-    <row r="5" ht="30.0" customHeight="1">
-      <c r="A5" s="65">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="54"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="54"/>
-    </row>
-    <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="65">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="54"/>
-    </row>
-    <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="65">
-        <v>3.0</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="67"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="67"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="67"/>
-      <c r="Y7" s="54"/>
-    </row>
-    <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="65">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="67"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="54"/>
-    </row>
-    <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="65">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="67"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="67"/>
-      <c r="Y9" s="54"/>
-    </row>
-    <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="67"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="67"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="67"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="67"/>
-      <c r="Y10" s="54"/>
-    </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="65" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="60"/>
+      <c r="Q11" s="61"/>
+      <c r="R11" s="59"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="59"/>
+      <c r="U11" s="61"/>
+      <c r="V11" s="59"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="59"/>
+      <c r="Y11" s="61"/>
+    </row>
+    <row r="12" spans="1:25" ht="28.5" customHeight="1">
+      <c r="A12" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="67"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="67"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="67"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="54"/>
-    </row>
-    <row r="12" ht="28.5" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="70"/>
-      <c r="X12" s="70"/>
-      <c r="Y12" s="71"/>
-    </row>
-    <row r="13" ht="36.0" customHeight="1"/>
-    <row r="14" ht="41.25" customHeight="1">
-      <c r="A14" s="50">
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
+      <c r="Y12" s="68"/>
+    </row>
+    <row r="13" spans="1:25" ht="36" customHeight="1"/>
+    <row r="14" spans="1:25" ht="41.25" customHeight="1">
+      <c r="A14" s="24">
         <f>'Invetario de Tablas'!A5</f>
         <v>2</v>
       </c>
-      <c r="B14" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="52" t="str">
+      <c r="B14" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="69" t="str">
         <f>'Invetario de Tablas'!B5</f>
         <v>ejemplo tabla 2</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="55" t="str">
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="71" t="str">
         <f>'Invetario de Tablas'!C5</f>
         <v>ejemplo derscripción tabla 2</v>
       </c>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="54"/>
-      <c r="X14" s="56" t="s">
+      <c r="L14" s="60"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y14" s="14"/>
+    </row>
+    <row r="15" spans="1:25" ht="32.25" customHeight="1">
+      <c r="A15" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="Y14" s="30"/>
-    </row>
-    <row r="15" ht="32.25" customHeight="1">
-      <c r="A15" s="57" t="s">
+      <c r="C15" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="S15" s="63"/>
+      <c r="T15" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="63"/>
+      <c r="V15" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" s="63"/>
+      <c r="X15" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="65"/>
+    </row>
+    <row r="16" spans="1:25" ht="30" customHeight="1">
+      <c r="A16" s="19">
         <v>1</v>
       </c>
-      <c r="B15" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="45"/>
+    </row>
+    <row r="17" spans="1:25" ht="30" customHeight="1">
+      <c r="A17" s="19">
+        <v>2</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="45"/>
+    </row>
+    <row r="18" spans="1:25" ht="30" customHeight="1">
+      <c r="A18" s="19">
+        <v>3</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="45"/>
+    </row>
+    <row r="19" spans="1:25" ht="30" customHeight="1">
+      <c r="A19" s="19">
+        <v>4</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="45"/>
+    </row>
+    <row r="20" spans="1:25" ht="30" customHeight="1">
+      <c r="A20" s="19">
+        <v>5</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="44"/>
+      <c r="Y20" s="45"/>
+    </row>
+    <row r="21" spans="1:25" ht="30" customHeight="1">
+      <c r="A21" s="20"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="45"/>
+    </row>
+    <row r="22" spans="1:25" ht="30" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="49"/>
+    </row>
+    <row r="23" spans="1:25" ht="48" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+    </row>
+    <row r="24" spans="1:25" ht="40.5" customHeight="1">
+      <c r="A24" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="N15" s="60"/>
-      <c r="O15" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S15" s="60"/>
-      <c r="T15" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="U15" s="60"/>
-      <c r="V15" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="W15" s="60"/>
-      <c r="X15" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y15" s="64"/>
-    </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="33"/>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="33"/>
-    </row>
-    <row r="18" ht="30.0" customHeight="1">
-      <c r="A18" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="33"/>
-    </row>
-    <row r="19" ht="30.0" customHeight="1">
-      <c r="A19" s="41">
-        <v>4.0</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="33"/>
-    </row>
-    <row r="20" ht="30.0" customHeight="1">
-      <c r="A20" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="33"/>
-    </row>
-    <row r="21" ht="30.0" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="33"/>
-    </row>
-    <row r="22" ht="30.0" customHeight="1">
-      <c r="A22" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="40"/>
-    </row>
-    <row r="23" ht="48.0" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-    </row>
-    <row r="24" ht="40.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="9"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="41"/>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -7275,29 +7986,102 @@
     <row r="971" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="137">
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:W3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="A24:Y24"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="O11:Q11"/>
@@ -7316,805 +8100,757 @@
     <mergeCell ref="K14:W14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="A24:Y24"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:W3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y971"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="28.38"/>
-    <col customWidth="1" min="3" max="3" width="28.75"/>
-    <col customWidth="1" min="4" max="9" width="3.88"/>
-    <col customWidth="1" min="10" max="10" width="27.63"/>
-    <col customWidth="1" min="11" max="22" width="3.88"/>
-    <col customWidth="1" min="23" max="23" width="4.63"/>
-    <col customWidth="1" min="24" max="24" width="17.0"/>
-    <col customWidth="1" min="25" max="25" width="30.38"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="9" width="3.88671875" customWidth="1"/>
+    <col min="10" max="10" width="27.6640625" customWidth="1"/>
+    <col min="11" max="22" width="3.88671875" customWidth="1"/>
+    <col min="23" max="23" width="4.6640625" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.0" customHeight="1">
-      <c r="A1" s="72" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" ht="28.5" customHeight="1"/>
-    <row r="3" ht="51.0" customHeight="1">
-      <c r="A3" s="50">
+    <row r="1" spans="1:25" ht="39" customHeight="1">
+      <c r="A1" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+    </row>
+    <row r="2" spans="1:25" ht="28.5" customHeight="1"/>
+    <row r="3" spans="1:25" ht="51" customHeight="1">
+      <c r="A3" s="24">
         <f>'Invetario de Tablas'!A4</f>
         <v>1</v>
       </c>
-      <c r="B3" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="25" t="str">
+      <c r="B3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="50" t="str">
         <f>'Invetario de Tablas'!B4</f>
         <v>ejemplo tabla 1</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="28" t="str">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="54" t="str">
         <f>'Invetario de Tablas'!C4</f>
         <v>ejemplo derscripción tabla 1</v>
       </c>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="75" t="s">
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="14"/>
+    </row>
+    <row r="4" spans="1:25" ht="37.5" customHeight="1">
+      <c r="A4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="30"/>
-    </row>
-    <row r="4" ht="37.5" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="C4" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="41"/>
+      <c r="T4" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="41"/>
+      <c r="V4" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="41"/>
+      <c r="X4" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="45"/>
+    </row>
+    <row r="5" spans="1:25" ht="30" customHeight="1">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="9"/>
-      <c r="X4" s="77" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="45"/>
+    </row>
+    <row r="6" spans="1:25" ht="30" customHeight="1">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="45"/>
+    </row>
+    <row r="7" spans="1:25" ht="30" customHeight="1">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="45"/>
+    </row>
+    <row r="8" spans="1:25" ht="30" customHeight="1">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="45"/>
+    </row>
+    <row r="9" spans="1:25" ht="30" customHeight="1">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="45"/>
+    </row>
+    <row r="10" spans="1:25" ht="30" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="45"/>
+    </row>
+    <row r="11" spans="1:25" ht="30" customHeight="1">
+      <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="33"/>
-    </row>
-    <row r="5" ht="30.0" customHeight="1">
-      <c r="A5" s="34">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="33"/>
-    </row>
-    <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="34">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="33"/>
-    </row>
-    <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="34">
-        <v>3.0</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="33"/>
-    </row>
-    <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="34">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="33"/>
-    </row>
-    <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="34">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="33"/>
-    </row>
-    <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="33"/>
-    </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="34" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="45"/>
+    </row>
+    <row r="12" spans="1:25" ht="28.5" customHeight="1">
+      <c r="A12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="33"/>
-    </row>
-    <row r="12" ht="28.5" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="40"/>
-    </row>
-    <row r="13" ht="36.0" customHeight="1"/>
-    <row r="14" ht="47.25" customHeight="1">
-      <c r="A14" s="50">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="49"/>
+    </row>
+    <row r="13" spans="1:25" ht="36" customHeight="1"/>
+    <row r="14" spans="1:25" ht="47.25" customHeight="1">
+      <c r="A14" s="24">
         <f>'Invetario de Tablas'!A5</f>
         <v>2</v>
       </c>
-      <c r="B14" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="52" t="str">
+      <c r="B14" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="69" t="str">
         <f>'Invetario de Tablas'!B5</f>
         <v>ejemplo tabla 2</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="55" t="str">
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="71" t="str">
         <f>'Invetario de Tablas'!C5</f>
         <v>ejemplo derscripción tabla 2</v>
       </c>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="54"/>
-      <c r="X14" s="78" t="s">
+      <c r="L14" s="60"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y14" s="14"/>
+    </row>
+    <row r="15" spans="1:25" ht="35.25" customHeight="1">
+      <c r="A15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Y14" s="30"/>
-    </row>
-    <row r="15" ht="35.25" customHeight="1">
-      <c r="A15" s="79" t="s">
+      <c r="C15" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="79"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="S15" s="76"/>
+      <c r="T15" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="76"/>
+      <c r="V15" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" s="76"/>
+      <c r="X15" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="45"/>
+    </row>
+    <row r="16" spans="1:25" ht="30" customHeight="1">
+      <c r="A16" s="19">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="80" t="s">
-        <v>41</v>
-      </c>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="80" t="s">
-        <v>42</v>
-      </c>
-      <c r="S15" s="82"/>
-      <c r="T15" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="U15" s="82"/>
-      <c r="V15" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="W15" s="82"/>
-      <c r="X15" s="77" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="45"/>
+    </row>
+    <row r="17" spans="1:25" ht="30" customHeight="1">
+      <c r="A17" s="19">
+        <v>2</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="45"/>
+    </row>
+    <row r="18" spans="1:25" ht="30" customHeight="1">
+      <c r="A18" s="19">
+        <v>3</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="45"/>
+    </row>
+    <row r="19" spans="1:25" ht="30" customHeight="1">
+      <c r="A19" s="19">
+        <v>4</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="45"/>
+    </row>
+    <row r="20" spans="1:25" ht="30" customHeight="1">
+      <c r="A20" s="19">
+        <v>5</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="44"/>
+      <c r="Y20" s="45"/>
+    </row>
+    <row r="21" spans="1:25" ht="30" customHeight="1">
+      <c r="A21" s="20"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="45"/>
+    </row>
+    <row r="22" spans="1:25" ht="30" customHeight="1">
+      <c r="A22" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="Y15" s="33"/>
-    </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="33"/>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="33"/>
-    </row>
-    <row r="18" ht="30.0" customHeight="1">
-      <c r="A18" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="33"/>
-    </row>
-    <row r="19" ht="30.0" customHeight="1">
-      <c r="A19" s="41">
-        <v>4.0</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="33"/>
-    </row>
-    <row r="20" ht="30.0" customHeight="1">
-      <c r="A20" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="33"/>
-    </row>
-    <row r="21" ht="30.0" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="33"/>
-    </row>
-    <row r="22" ht="30.0" customHeight="1">
-      <c r="A22" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="40"/>
-    </row>
-    <row r="23" ht="48.0" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-    </row>
-    <row r="24" ht="40.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="9"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="49"/>
+    </row>
+    <row r="23" spans="1:25" ht="48" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+    </row>
+    <row r="24" spans="1:25" ht="40.5" customHeight="1">
+      <c r="A24" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="41"/>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -9056,29 +9792,102 @@
     <row r="971" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="137">
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:W3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="A24:Y24"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="O11:Q11"/>
@@ -9097,103 +9906,30 @@
     <mergeCell ref="K14:W14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="A24:Y24"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:W3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>